--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.2595275334217</v>
+        <v>1.992173224181026</v>
       </c>
       <c r="D2" t="n">
-        <v>13.24995072026853</v>
+        <v>2.153116992043637</v>
       </c>
       <c r="E2" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F2" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.41233185427479</v>
+        <v>5.592003926319654</v>
       </c>
       <c r="D3" t="n">
-        <v>35.42065343196347</v>
+        <v>5.755856182694065</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F3" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.12004267964097</v>
+        <v>3.919506935441659</v>
       </c>
       <c r="D4" t="n">
-        <v>25.1127130868384</v>
+        <v>4.08081587661124</v>
       </c>
       <c r="E4" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F4" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.053291425203307</v>
+        <v>1.471159856595537</v>
       </c>
       <c r="D5" t="n">
-        <v>9.817595938866072</v>
+        <v>1.595359340065737</v>
       </c>
       <c r="E5" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F5" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.15067816432999</v>
+        <v>6.361985201703623</v>
       </c>
       <c r="D6" t="n">
-        <v>38.94933920768593</v>
+        <v>6.329267621248964</v>
       </c>
       <c r="E6" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F6" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.60216275834672</v>
+        <v>5.785351448231341</v>
       </c>
       <c r="D7" t="n">
-        <v>35.86291817575407</v>
+        <v>5.827724203560036</v>
       </c>
       <c r="E7" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F7" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.14189434859161</v>
+        <v>5.223057831646136</v>
       </c>
       <c r="D8" t="n">
-        <v>31.92713409607016</v>
+        <v>5.1881592906114</v>
       </c>
       <c r="E8" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F8" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.21053102431445</v>
+        <v>4.909211291451098</v>
       </c>
       <c r="D9" t="n">
-        <v>29.98087269413214</v>
+        <v>4.871891812796473</v>
       </c>
       <c r="E9" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F9" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4.121330911184979</v>
+        <v>0.669716273067559</v>
       </c>
       <c r="D10" t="n">
-        <v>3.917461059355718</v>
+        <v>0.6365874221453043</v>
       </c>
       <c r="E10" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F10" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.38159681172304</v>
+        <v>3.474509481904994</v>
       </c>
       <c r="D11" t="n">
-        <v>21.27372694550516</v>
+        <v>3.456980628644589</v>
       </c>
       <c r="E11" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F11" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.40593229893512</v>
+        <v>5.103463998576957</v>
       </c>
       <c r="D12" t="n">
-        <v>31.55166085430616</v>
+        <v>5.127144888824752</v>
       </c>
       <c r="E12" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F12" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.02185826409359</v>
+        <v>6.34105196791521</v>
       </c>
       <c r="D13" t="n">
-        <v>38.93930967387676</v>
+        <v>6.327637822004974</v>
       </c>
       <c r="E13" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F13" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.12038433303032</v>
+        <v>6.357062454117428</v>
       </c>
       <c r="D14" t="n">
-        <v>39.2840560145425</v>
+        <v>6.383659102363157</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F14" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>44.71266538533632</v>
+        <v>7.265808125117153</v>
       </c>
       <c r="D15" t="n">
-        <v>44.94267984408366</v>
+        <v>7.303185474663596</v>
       </c>
       <c r="E15" t="n">
-        <v>11.99865791995745</v>
+        <v>1.949781911993085</v>
       </c>
       <c r="F15" t="n">
-        <v>11.89137273775338</v>
+        <v>1.932348069884925</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
